--- a/data/source-participacon-momoento4-planeacion-teritorial/Participacion2026-31-08-all.xlsx
+++ b/data/source-participacon-momoento4-planeacion-teritorial/Participacion2026-31-08-all.xlsx
@@ -123,9 +123,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿ Light"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿ Light"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,9 +158,9 @@
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -489,7 +489,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z2" t="str">
-        <v>bdguzman@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="3" ht="180" customHeight="1">
@@ -554,7 +554,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z3" t="str">
-        <v>kvirviescas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="4" ht="180" customHeight="1">
@@ -625,7 +625,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z4" t="str">
-        <v>jernestoherrera@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="5" ht="180" customHeight="1">
@@ -690,7 +690,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z5" t="str">
-        <v>evbello@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="6" ht="180" customHeight="1">
@@ -755,7 +755,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z6" t="str">
-        <v>jsavila@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="7" ht="180" customHeight="1">
@@ -826,7 +826,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN CHÍA</v>
       </c>
       <c r="Z7" t="str">
-        <v>joselrodriguezr@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="8" ht="180" customHeight="1">
@@ -891,7 +891,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z8" t="str">
-        <v>recorredor@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="9" ht="180" customHeight="1">
@@ -953,7 +953,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN SOACHA</v>
       </c>
       <c r="Z9" t="str">
-        <v>japaramo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="10" ht="180" customHeight="1">
@@ -1015,7 +1015,7 @@
         <v>UNIDAD REGIONAL, SEDE FUSAGASUGÁ</v>
       </c>
       <c r="Z10" t="str">
-        <v>yytovar@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="11" ht="180" customHeight="1">
@@ -1077,7 +1077,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z11" t="str">
-        <v>yfhuertas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="12" ht="180" customHeight="1">
@@ -1148,7 +1148,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z12" t="str">
-        <v>calexispachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="13" ht="180" customHeight="1">
@@ -1213,7 +1213,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z13" t="str">
-        <v>celaverde@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="14" ht="180" customHeight="1">
@@ -1284,7 +1284,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z14" t="str">
-        <v>ytperilla@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="15" ht="180" customHeight="1">
@@ -1355,7 +1355,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z15" t="str">
-        <v>caguarin@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="16" ht="180" customHeight="1">
@@ -1420,7 +1420,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z16" t="str">
-        <v>candresrodriguezm@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="17" ht="180" customHeight="1">
@@ -1485,7 +1485,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z17" t="str">
-        <v>dcarolinasantamaria@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="18" ht="180" customHeight="1">
@@ -1547,7 +1547,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z18" t="str">
-        <v>jvtorres@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="19" ht="180" customHeight="1">
@@ -1618,7 +1618,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z19" t="str">
-        <v>raparra@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="20" ht="180" customHeight="1">
@@ -1683,7 +1683,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z20" t="str">
-        <v>dmcarpeta@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="21" ht="180" customHeight="1">
@@ -1745,7 +1745,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z21" t="str">
-        <v>laugustogonzalez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="22" ht="180" customHeight="1">
@@ -1810,7 +1810,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z22" t="str">
-        <v>anasrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="23" ht="180" customHeight="1">
@@ -1875,7 +1875,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z23" t="str">
-        <v>rdelosangelesballesteros@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="24" ht="180" customHeight="1">
@@ -1946,7 +1946,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z24" t="str">
-        <v>ocroswaithe@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="25" ht="180" customHeight="1">
@@ -2017,7 +2017,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z25" t="str">
-        <v>daortiz@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="26" ht="180" customHeight="1">
@@ -2082,7 +2082,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z26" t="str">
-        <v>dbajonero@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="27" ht="180" customHeight="1">
@@ -2147,7 +2147,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z27" t="str">
-        <v>cgarciam@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="28" ht="180" customHeight="1">
@@ -2212,7 +2212,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z28" t="str">
-        <v>dricardovargas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="29" ht="180" customHeight="1">
@@ -2283,7 +2283,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z29" t="str">
-        <v>lnvenegas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="30" ht="180" customHeight="1">
@@ -2354,7 +2354,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z30" t="str">
-        <v>adcaro@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="31" ht="180" customHeight="1">
@@ -2425,7 +2425,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z31" t="str">
-        <v>jcarlosramos@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="32" ht="180" customHeight="1">
@@ -2496,7 +2496,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z32" t="str">
-        <v>afcely@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="33" ht="180" customHeight="1">
@@ -2561,7 +2561,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z33" t="str">
-        <v>jfreddyromero@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="34" ht="180" customHeight="1">
@@ -2632,7 +2632,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z34" t="str">
-        <v>achibuque@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="35" ht="180" customHeight="1">
@@ -2697,7 +2697,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z35" t="str">
-        <v>sgomezm@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="36" ht="180" customHeight="1">
@@ -2762,7 +2762,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z36" t="str">
-        <v>iyrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="37" ht="180" customHeight="1">
@@ -2833,7 +2833,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z37" t="str">
-        <v>jsforerojaramillo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="38" ht="180" customHeight="1">
@@ -2898,7 +2898,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z38" t="str">
-        <v>hsmedina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="39" ht="180" customHeight="1">
@@ -2969,7 +2969,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z39" t="str">
-        <v>sbarco@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="40" ht="180" customHeight="1">
@@ -3034,7 +3034,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z40" t="str">
-        <v>nccely@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="41" ht="180" customHeight="1">
@@ -3099,7 +3099,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z41" t="str">
-        <v>vcadena@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="42" ht="180" customHeight="1">
@@ -3164,7 +3164,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z42" t="str">
-        <v>algarnica@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="43" ht="180" customHeight="1">
@@ -3229,7 +3229,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z43" t="str">
-        <v>diegoandresleon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="44" ht="180" customHeight="1">
@@ -3300,7 +3300,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z44" t="str">
-        <v>oalejandrobeltran@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="45" ht="180" customHeight="1">
@@ -3365,7 +3365,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z45" t="str">
-        <v>cristiandtorres@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="46" ht="180" customHeight="1">
@@ -3430,7 +3430,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z46" t="str">
-        <v>bscontreras@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="47" ht="180" customHeight="1">
@@ -3495,7 +3495,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z47" t="str">
-        <v>mandrespacheco@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="48" ht="180" customHeight="1">
@@ -3560,7 +3560,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z48" t="str">
-        <v>cdmedina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="49" ht="180" customHeight="1">
@@ -3631,7 +3631,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z49" t="str">
-        <v>rr.rodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="50" ht="180" customHeight="1">
@@ -3696,7 +3696,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z50" t="str">
-        <v>mcamilarincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="51" ht="180" customHeight="1">
@@ -3761,7 +3761,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z51" t="str">
-        <v>plgil@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="52" ht="180" customHeight="1">
@@ -3826,7 +3826,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z52" t="str">
-        <v>ritorres@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="53" ht="180" customHeight="1">
@@ -3891,7 +3891,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z53" t="str">
-        <v>jestebanchacon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="54" ht="180" customHeight="1">
@@ -3962,7 +3962,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z54" t="str">
-        <v>drtroncoso@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="55" ht="180" customHeight="1">
@@ -4027,7 +4027,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z55" t="str">
-        <v>ymaritzarocha@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="56" ht="180" customHeight="1">
@@ -4098,7 +4098,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z56" t="str">
-        <v>nffernandez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="57" ht="180" customHeight="1">
@@ -4169,7 +4169,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z57" t="str">
-        <v>caugustosanabria@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="58" ht="180" customHeight="1">
@@ -4234,7 +4234,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z58" t="str">
-        <v>mguaje@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="59" ht="180" customHeight="1">
@@ -4299,7 +4299,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z59" t="str">
-        <v>anyelamartinez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="60" ht="180" customHeight="1">
@@ -4361,7 +4361,7 @@
         <v>UNIDAD REGIONAL, SEDE FUSAGASUGÁ</v>
       </c>
       <c r="Z60" t="str">
-        <v>panaranjo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="61" ht="180" customHeight="1">
@@ -4432,7 +4432,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z61" t="str">
-        <v>dctovar@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="62" ht="180" customHeight="1">
@@ -4497,7 +4497,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z62" t="str">
-        <v>dfelipegomez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="63" ht="180" customHeight="1">
@@ -4568,7 +4568,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z63" t="str">
-        <v>oalvarado@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="64" ht="180" customHeight="1">
@@ -4639,7 +4639,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z64" t="str">
-        <v>sealdana@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="65" ht="180" customHeight="1">
@@ -4704,7 +4704,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z65" t="str">
-        <v>ssofiacampos@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="66" ht="180" customHeight="1">
@@ -4766,7 +4766,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z66" t="str">
-        <v>lpereiraf@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="67" ht="180" customHeight="1">
@@ -4831,7 +4831,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z67" t="str">
-        <v>sfarias@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="68" ht="180" customHeight="1">
@@ -4902,7 +4902,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z68" t="str">
-        <v>acastrillonm@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="69" ht="180" customHeight="1">
@@ -4973,7 +4973,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z69" t="str">
-        <v>aplaza@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="70" ht="180" customHeight="1">
@@ -5038,7 +5038,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z70" t="str">
-        <v>abustosp@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
     <row r="71" ht="180" customHeight="1">
@@ -5103,7 +5103,7 @@
         <v>UNIDAD REGIONAL, EXTENSIÓN ZIPAQUIRÁ</v>
       </c>
       <c r="Z71" t="str">
-        <v>idrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
     </row>
   </sheetData>
